--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88617</v>
+        <v>88709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128487910</v>
       </c>
       <c r="B4" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128488780</v>
       </c>
       <c r="B5" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B8" t="n">
-        <v>80136</v>
+        <v>91470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R8" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B9" t="n">
-        <v>91378</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R9" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>97561</v>
+        <v>88669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R10" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1573,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>88577</v>
+        <v>97654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,37 +1608,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R11" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,13 +1676,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128487910</v>
+        <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>75171</v>
+        <v>88853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403895</v>
+        <v>403789</v>
       </c>
       <c r="R4" t="n">
-        <v>7029243</v>
+        <v>7029299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128488780</v>
+        <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>88853</v>
+        <v>75171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403789</v>
+        <v>403895</v>
       </c>
       <c r="R5" t="n">
-        <v>7029299</v>
+        <v>7029243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>88669</v>
+        <v>97654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,37 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R10" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,13 +1570,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>97654</v>
+        <v>88669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,34 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R11" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1675,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88709</v>
+        <v>88715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R8" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>91476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R9" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>97654</v>
+        <v>88675</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R10" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1573,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>88669</v>
+        <v>97660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,37 +1608,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R11" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,13 +1676,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88715</v>
+        <v>88721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>91482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R8" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R9" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
         <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>88675</v>
+        <v>88681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128488780</v>
+        <v>128487910</v>
       </c>
       <c r="B4" t="n">
-        <v>88865</v>
+        <v>75177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403789</v>
+        <v>403895</v>
       </c>
       <c r="R4" t="n">
-        <v>7029299</v>
+        <v>7029243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128487910</v>
+        <v>128488780</v>
       </c>
       <c r="B5" t="n">
-        <v>75175</v>
+        <v>88867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403895</v>
+        <v>403789</v>
       </c>
       <c r="R5" t="n">
-        <v>7029243</v>
+        <v>7029299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>91482</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R8" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R9" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>88681</v>
+        <v>97668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,37 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R10" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,13 +1570,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>97666</v>
+        <v>88683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,34 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R11" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1675,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128487910</v>
+        <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>75177</v>
+        <v>88867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403895</v>
+        <v>403789</v>
       </c>
       <c r="R4" t="n">
-        <v>7029243</v>
+        <v>7029299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128488780</v>
+        <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>88867</v>
+        <v>75177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403789</v>
+        <v>403895</v>
       </c>
       <c r="R5" t="n">
-        <v>7029299</v>
+        <v>7029243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>97668</v>
+        <v>88683</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R10" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1573,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>88683</v>
+        <v>97669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,37 +1608,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R11" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,13 +1676,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88723</v>
+        <v>88750</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>88683</v>
+        <v>97696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,37 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R10" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,13 +1570,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>97669</v>
+        <v>88710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,34 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R11" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1675,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92446</v>
+        <v>92451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88750</v>
+        <v>88754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>88710</v>
+        <v>88714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88899</v>
+        <v>88904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B8" t="n">
-        <v>80226</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R8" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B9" t="n">
-        <v>91517</v>
+        <v>80226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R9" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
         <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>88714</v>
+        <v>88715</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>80226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R8" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>80226</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R9" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>97709</v>
+        <v>88715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R10" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1573,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>88715</v>
+        <v>97709</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,37 +1608,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R11" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,13 +1676,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>88904</v>
+        <v>88908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>88715</v>
+        <v>88719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R8" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>80230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R9" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128488780</v>
+        <v>128487910</v>
       </c>
       <c r="B4" t="n">
-        <v>88908</v>
+        <v>75209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403789</v>
+        <v>403895</v>
       </c>
       <c r="R4" t="n">
-        <v>7029299</v>
+        <v>7029243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128487910</v>
+        <v>128488780</v>
       </c>
       <c r="B5" t="n">
-        <v>75209</v>
+        <v>88908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403895</v>
+        <v>403789</v>
       </c>
       <c r="R5" t="n">
-        <v>7029243</v>
+        <v>7029299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128488914</v>
+        <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403766</v>
+        <v>403873</v>
       </c>
       <c r="R8" t="n">
-        <v>7029177</v>
+        <v>7029308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128489607</v>
+        <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>80230</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403873</v>
+        <v>403766</v>
       </c>
       <c r="R9" t="n">
-        <v>7029308</v>
+        <v>7029177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>88719</v>
+        <v>97713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,37 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R10" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,13 +1570,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1597,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B11" t="n">
-        <v>97713</v>
+        <v>88719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,34 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R11" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1675,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488336</v>
       </c>
       <c r="B2" t="n">
-        <v>92460</v>
+        <v>92465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128488790</v>
       </c>
       <c r="B3" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128487910</v>
+        <v>128488780</v>
       </c>
       <c r="B4" t="n">
-        <v>75209</v>
+        <v>88913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403895</v>
+        <v>403789</v>
       </c>
       <c r="R4" t="n">
-        <v>7029243</v>
+        <v>7029299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128488780</v>
+        <v>128487910</v>
       </c>
       <c r="B5" t="n">
-        <v>88908</v>
+        <v>83005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403789</v>
+        <v>403895</v>
       </c>
       <c r="R5" t="n">
-        <v>7029299</v>
+        <v>7029243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128487874</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128489607</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128488914</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128488834</v>
+        <v>128489393</v>
       </c>
       <c r="B10" t="n">
-        <v>97713</v>
+        <v>88724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220686</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403791</v>
+        <v>403717</v>
       </c>
       <c r="R10" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,12 +1573,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128489393</v>
+        <v>128488834</v>
       </c>
       <c r="B11" t="n">
-        <v>88719</v>
+        <v>97720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,37 +1608,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4394</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403717</v>
+        <v>403791</v>
       </c>
       <c r="R11" t="n">
-        <v>7029191</v>
+        <v>7029243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,13 +1676,12 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
+          <t>Grovvuxen grannaturkskog i nordsluttning</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128488336</v>
+        <v>128488780</v>
       </c>
       <c r="B2" t="n">
-        <v>92468</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4787</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403853</v>
+        <v>403789</v>
       </c>
       <c r="R2" t="n">
-        <v>7029246</v>
+        <v>7029299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128488790</v>
+        <v>128489607</v>
       </c>
       <c r="B3" t="n">
-        <v>88766</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403804</v>
+        <v>403873</v>
       </c>
       <c r="R3" t="n">
-        <v>7029290</v>
+        <v>7029308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,45 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128487910</v>
+        <v>128489393</v>
       </c>
       <c r="B4" t="n">
-        <v>83005</v>
+        <v>89106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>4394</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Klingruthögen, Klingruthögen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403895</v>
+        <v>403717</v>
       </c>
       <c r="R4" t="n">
-        <v>7029243</v>
+        <v>7029191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,12 +961,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grovvuxen grannaturkskog i nordsluttning</t>
+          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -981,32 +985,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128488780</v>
+        <v>128488790</v>
       </c>
       <c r="B5" t="n">
-        <v>88915</v>
+        <v>89143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>4405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403789</v>
+        <v>403804</v>
       </c>
       <c r="R5" t="n">
-        <v>7029299</v>
+        <v>7029290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1090,7 @@
         <v>128487868</v>
       </c>
       <c r="B6" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,32 +1189,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128487874</v>
+        <v>128488336</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>92886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403939</v>
+        <v>403853</v>
       </c>
       <c r="R7" t="n">
-        <v>7029284</v>
+        <v>7029246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128489607</v>
+        <v>128487874</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403873</v>
+        <v>403939</v>
       </c>
       <c r="R8" t="n">
-        <v>7029308</v>
+        <v>7029284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128488914</v>
+        <v>128487910</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403766</v>
+        <v>403895</v>
       </c>
       <c r="R9" t="n">
-        <v>7029177</v>
+        <v>7029243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1498,7 @@
         <v>128488834</v>
       </c>
       <c r="B10" t="n">
-        <v>97723</v>
+        <v>98194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,112 +1594,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>128489393</v>
-      </c>
-      <c r="B11" t="n">
-        <v>88726</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Honungsvaxing</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Klingruthögen, Klingruthögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>403717</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7029191</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Fjällbjörkskog med inslag av gran på gräs-och örtrik mark</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17095-2025 artfynd.xlsx
+++ b/artfynd/A 17095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128489607</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128489393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487868</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487874</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487910</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,8 +1639,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>